--- a/dados/SURVEY_BACKUP/SURVEY_CBO_20260802.xlsx
+++ b/dados/SURVEY_BACKUP/SURVEY_CBO_20260802.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_BACKUP/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{C3F2CE38-7425-4AB2-A381-91F05DC8FDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="988" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="8880" tabRatio="988" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
